--- a/2022 data/excel_outputs/264_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/264_boothwise_data.xlsx
@@ -14,11 +14,86 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="447">
   <si>
     <t>AC 264 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
+    <t>Unnamed: 23</t>
+  </si>
+  <si>
+    <t>Unnamed: 24</t>
+  </si>
+  <si>
+    <t>Unnamed: 25</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
@@ -604,7 +679,7 @@
     <t>RANJEET PANDIT I.CO. LOHGARA ROOM N. 4</t>
   </si>
   <si>
-    <t>RANJEET PANDIT I.CO. LOHGARA ROOM N. ■</t>
+    <t>KRRISHAK I0KA0 GADAI़YA KALAM MADHY BHAG</t>
   </si>
   <si>
     <t>P.V. CHANDRA LONIYAN</t>
@@ -1286,8 +1361,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1303,7 +1386,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1311,12 +1394,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1615,88 +1716,163 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:26">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:26">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>399</v>
+        <v>424</v>
       </c>
       <c r="D2" t="s">
-        <v>400</v>
+        <v>425</v>
       </c>
       <c r="E2" t="s">
-        <v>401</v>
+        <v>426</v>
       </c>
       <c r="F2" t="s">
-        <v>402</v>
+        <v>427</v>
       </c>
       <c r="G2" t="s">
-        <v>403</v>
+        <v>428</v>
       </c>
       <c r="H2" t="s">
-        <v>404</v>
+        <v>429</v>
       </c>
       <c r="I2" t="s">
-        <v>405</v>
+        <v>430</v>
       </c>
       <c r="J2" t="s">
-        <v>406</v>
+        <v>431</v>
       </c>
       <c r="K2" t="s">
-        <v>407</v>
+        <v>432</v>
       </c>
       <c r="L2" t="s">
-        <v>408</v>
+        <v>433</v>
       </c>
       <c r="M2" t="s">
-        <v>409</v>
+        <v>434</v>
       </c>
       <c r="N2" t="s">
-        <v>410</v>
+        <v>435</v>
       </c>
       <c r="O2" t="s">
-        <v>411</v>
+        <v>436</v>
       </c>
       <c r="P2" t="s">
-        <v>412</v>
+        <v>437</v>
       </c>
       <c r="Q2" t="s">
-        <v>413</v>
+        <v>438</v>
       </c>
       <c r="R2" t="s">
-        <v>414</v>
+        <v>439</v>
       </c>
       <c r="S2" t="s">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="T2" t="s">
-        <v>416</v>
+        <v>441</v>
       </c>
       <c r="U2" t="s">
-        <v>417</v>
+        <v>442</v>
       </c>
       <c r="V2" t="s">
-        <v>418</v>
+        <v>443</v>
       </c>
       <c r="W2" t="s">
-        <v>419</v>
+        <v>444</v>
       </c>
       <c r="X2" t="s">
-        <v>419</v>
+        <v>444</v>
       </c>
       <c r="Y2" t="s">
-        <v>420</v>
+        <v>445</v>
       </c>
       <c r="Z2" t="s">
-        <v>421</v>
+        <v>446</v>
       </c>
     </row>
     <row r="3" spans="1:26">
@@ -1704,7 +1880,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="C3">
         <v>991</v>
@@ -1784,7 +1960,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="C4">
         <v>928</v>
@@ -1864,7 +2040,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="C5">
         <v>961</v>
@@ -1944,7 +2120,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="C6">
         <v>596</v>
@@ -2024,7 +2200,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C7">
         <v>745</v>
@@ -2104,7 +2280,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="C8">
         <v>981</v>
@@ -2184,7 +2360,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C9">
         <v>725</v>
@@ -2264,7 +2440,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="C10">
         <v>760</v>
@@ -2344,7 +2520,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="C11">
         <v>1098</v>
@@ -2424,7 +2600,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="C12">
         <v>1109</v>
@@ -2504,7 +2680,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C13">
         <v>990</v>
@@ -2584,7 +2760,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="C14">
         <v>1052</v>
@@ -2664,7 +2840,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C15">
         <v>1067</v>
@@ -2744,7 +2920,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C16">
         <v>1035</v>
@@ -2824,7 +3000,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="C17">
         <v>921</v>
@@ -2904,7 +3080,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="C18">
         <v>1182</v>
@@ -2984,7 +3160,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="C19">
         <v>789</v>
@@ -3064,7 +3240,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C20">
         <v>970</v>
@@ -3144,7 +3320,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="C21">
         <v>941</v>
@@ -3224,7 +3400,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="C22">
         <v>964</v>
@@ -3304,7 +3480,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="C23">
         <v>816</v>
@@ -3384,7 +3560,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C24">
         <v>925</v>
@@ -3464,7 +3640,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="C25">
         <v>1082</v>
@@ -3544,7 +3720,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="C26">
         <v>1103</v>
@@ -3624,7 +3800,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="C27">
         <v>1120</v>
@@ -3704,7 +3880,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="C28">
         <v>964</v>
@@ -3784,7 +3960,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="C29">
         <v>539</v>
@@ -3864,7 +4040,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C30">
         <v>821</v>
@@ -3944,7 +4120,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C31">
         <v>797</v>
@@ -4024,7 +4200,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="C32">
         <v>526</v>
@@ -4104,7 +4280,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C33">
         <v>745</v>
@@ -4184,7 +4360,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="C34">
         <v>1080</v>
@@ -4264,7 +4440,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="C35">
         <v>618</v>
@@ -4344,7 +4520,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="C36">
         <v>1005</v>
@@ -4424,7 +4600,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="C37">
         <v>943</v>
@@ -4504,7 +4680,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="C38">
         <v>781</v>
@@ -4584,7 +4760,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="C39">
         <v>783</v>
@@ -4664,7 +4840,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="C40">
         <v>721</v>
@@ -4744,7 +4920,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="C41">
         <v>705</v>
@@ -4824,7 +5000,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="C42">
         <v>750</v>
@@ -4904,7 +5080,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="C43">
         <v>727</v>
@@ -4984,7 +5160,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="C44">
         <v>802</v>
@@ -5064,7 +5240,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="C45">
         <v>677</v>
@@ -5144,7 +5320,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="C46">
         <v>643</v>
@@ -5224,7 +5400,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="C47">
         <v>839</v>
@@ -5304,7 +5480,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="C48">
         <v>776</v>
@@ -5384,7 +5560,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="C49">
         <v>743</v>
@@ -5464,7 +5640,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="C50">
         <v>1117</v>
@@ -5544,7 +5720,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="C51">
         <v>940</v>
@@ -5624,7 +5800,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="C52">
         <v>1078</v>
@@ -5704,7 +5880,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="C53">
         <v>888</v>
@@ -5784,7 +5960,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="C54">
         <v>794</v>
@@ -5864,7 +6040,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="C55">
         <v>991</v>
@@ -5944,7 +6120,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C56">
         <v>650</v>
@@ -6024,7 +6200,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="C57">
         <v>823</v>
@@ -6104,7 +6280,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="C58">
         <v>953</v>
@@ -6184,7 +6360,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="C59">
         <v>1185</v>
@@ -6264,7 +6440,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="C60">
         <v>1120</v>
@@ -6344,7 +6520,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="C61">
         <v>1041</v>
@@ -6424,7 +6600,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="C62">
         <v>1204</v>
@@ -6504,7 +6680,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="C63">
         <v>1168</v>
@@ -6584,7 +6760,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="C64">
         <v>780</v>
@@ -6664,7 +6840,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="C65">
         <v>770</v>
@@ -6744,7 +6920,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="C66">
         <v>894</v>
@@ -6824,7 +7000,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="C67">
         <v>871</v>
@@ -6904,7 +7080,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="C68">
         <v>1117</v>
@@ -6984,7 +7160,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="C69">
         <v>1080</v>
@@ -7064,7 +7240,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="C70">
         <v>848</v>
@@ -7144,7 +7320,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="C71">
         <v>879</v>
@@ -7224,7 +7400,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="C72">
         <v>801</v>
@@ -7304,7 +7480,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="C73">
         <v>698</v>
@@ -7384,7 +7560,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="C74">
         <v>747</v>
@@ -7464,7 +7640,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="C75">
         <v>1004</v>
@@ -7544,7 +7720,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="C76">
         <v>745</v>
@@ -7624,7 +7800,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="C77">
         <v>1037</v>
@@ -7704,7 +7880,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="C78">
         <v>783</v>
@@ -7784,7 +7960,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="C79">
         <v>609</v>
@@ -7864,7 +8040,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="C80">
         <v>625</v>
@@ -7944,7 +8120,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="C81">
         <v>983</v>
@@ -8024,7 +8200,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="C82">
         <v>981</v>
@@ -8104,7 +8280,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="C83">
         <v>895</v>
@@ -8184,7 +8360,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="C84">
         <v>918</v>
@@ -8264,7 +8440,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="C85">
         <v>1047</v>
@@ -8344,7 +8520,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="C86">
         <v>1044</v>
@@ -8424,7 +8600,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="C87">
         <v>991</v>
@@ -8504,7 +8680,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="C88">
         <v>1065</v>
@@ -8584,7 +8760,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="C89">
         <v>838</v>
@@ -8664,7 +8840,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="C90">
         <v>717</v>
@@ -8744,7 +8920,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="C91">
         <v>1057</v>
@@ -8824,7 +9000,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C92">
         <v>1060</v>
@@ -8904,7 +9080,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="C93">
         <v>1033</v>
@@ -8984,7 +9160,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="C94">
         <v>760</v>
@@ -9064,7 +9240,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="C95">
         <v>686</v>
@@ -9144,7 +9320,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="C96">
         <v>626</v>
@@ -9224,7 +9400,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="C97">
         <v>778</v>
@@ -9304,7 +9480,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="C98">
         <v>943</v>
@@ -9384,7 +9560,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="C99">
         <v>747</v>
@@ -9464,7 +9640,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="C100">
         <v>817</v>
@@ -9544,7 +9720,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="C101">
         <v>747</v>
@@ -9624,7 +9800,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="C102">
         <v>907</v>
@@ -9704,7 +9880,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="C103">
         <v>481</v>
@@ -9784,7 +9960,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="C104">
         <v>785</v>
@@ -9864,7 +10040,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="C105">
         <v>835</v>
@@ -9944,7 +10120,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="C106">
         <v>858</v>
@@ -10024,7 +10200,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="C107">
         <v>853</v>
@@ -10104,7 +10280,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="C108">
         <v>615</v>
@@ -10184,7 +10360,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="C109">
         <v>822</v>
@@ -10264,7 +10440,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="C110">
         <v>825</v>
@@ -10344,7 +10520,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="C111">
         <v>868</v>
@@ -10424,7 +10600,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="C112">
         <v>838</v>
@@ -10504,7 +10680,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="C113">
         <v>930</v>
@@ -10584,7 +10760,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="C114">
         <v>759</v>
@@ -10664,7 +10840,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="C115">
         <v>488</v>
@@ -10744,7 +10920,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="C116">
         <v>698</v>
@@ -10824,7 +11000,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="C117">
         <v>716</v>
@@ -10904,7 +11080,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="C118">
         <v>779</v>
@@ -10984,7 +11160,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="C119">
         <v>640</v>
@@ -11064,7 +11240,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="C120">
         <v>420</v>
@@ -11144,7 +11320,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="C121">
         <v>642</v>
@@ -11224,7 +11400,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>119</v>
+        <v>144</v>
       </c>
       <c r="C122">
         <v>611</v>
@@ -11304,7 +11480,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="C123">
         <v>503</v>
@@ -11384,7 +11560,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="C124">
         <v>618</v>
@@ -11464,7 +11640,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="C125">
         <v>1019</v>
@@ -11544,7 +11720,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="C126">
         <v>849</v>
@@ -11624,7 +11800,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="C127">
         <v>680</v>
@@ -11704,7 +11880,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="C128">
         <v>575</v>
@@ -11784,7 +11960,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="C129">
         <v>715</v>
@@ -11864,7 +12040,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>127</v>
+        <v>152</v>
       </c>
       <c r="C130">
         <v>733</v>
@@ -11944,7 +12120,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>128</v>
+        <v>153</v>
       </c>
       <c r="C131">
         <v>813</v>
@@ -12024,7 +12200,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="C132">
         <v>701</v>
@@ -12104,7 +12280,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>130</v>
+        <v>155</v>
       </c>
       <c r="C133">
         <v>909</v>
@@ -12184,7 +12360,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>131</v>
+        <v>156</v>
       </c>
       <c r="C134">
         <v>725</v>
@@ -12264,7 +12440,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>132</v>
+        <v>157</v>
       </c>
       <c r="C135">
         <v>964</v>
@@ -12344,7 +12520,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>133</v>
+        <v>158</v>
       </c>
       <c r="C136">
         <v>615</v>
@@ -12424,7 +12600,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="C137">
         <v>691</v>
@@ -12504,7 +12680,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="C138">
         <v>713</v>
@@ -12584,7 +12760,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="C139">
         <v>708</v>
@@ -12664,7 +12840,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="C140">
         <v>823</v>
@@ -12744,7 +12920,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="C141">
         <v>1003</v>
@@ -12824,7 +13000,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="C142">
         <v>819</v>
@@ -12904,7 +13080,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="C143">
         <v>734</v>
@@ -12984,7 +13160,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="C144">
         <v>812</v>
@@ -13064,7 +13240,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="C145">
         <v>735</v>
@@ -13144,7 +13320,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>143</v>
+        <v>168</v>
       </c>
       <c r="C146">
         <v>660</v>
@@ -13224,7 +13400,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>144</v>
+        <v>169</v>
       </c>
       <c r="C147">
         <v>752</v>
@@ -13304,7 +13480,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="C148">
         <v>873</v>
@@ -13384,7 +13560,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>146</v>
+        <v>171</v>
       </c>
       <c r="C149">
         <v>791</v>
@@ -13464,7 +13640,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="C150">
         <v>669</v>
@@ -13544,7 +13720,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="C151">
         <v>1125</v>
@@ -13624,7 +13800,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>149</v>
+        <v>174</v>
       </c>
       <c r="C152">
         <v>976</v>
@@ -13704,7 +13880,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="C153">
         <v>500</v>
@@ -13784,7 +13960,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>151</v>
+        <v>176</v>
       </c>
       <c r="C154">
         <v>767</v>
@@ -13864,7 +14040,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="C155">
         <v>681</v>
@@ -13944,7 +14120,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>153</v>
+        <v>178</v>
       </c>
       <c r="C156">
         <v>1087</v>
@@ -14024,7 +14200,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="C157">
         <v>959</v>
@@ -14104,7 +14280,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="C158">
         <v>929</v>
@@ -14184,7 +14360,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="C159">
         <v>859</v>
@@ -14264,7 +14440,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="C160">
         <v>951</v>
@@ -14344,7 +14520,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>158</v>
+        <v>183</v>
       </c>
       <c r="C161">
         <v>559</v>
@@ -14424,7 +14600,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>159</v>
+        <v>184</v>
       </c>
       <c r="C162">
         <v>424</v>
@@ -14504,7 +14680,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="C163">
         <v>641</v>
@@ -14584,7 +14760,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>161</v>
+        <v>186</v>
       </c>
       <c r="C164">
         <v>634</v>
@@ -14664,7 +14840,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>162</v>
+        <v>187</v>
       </c>
       <c r="C165">
         <v>1079</v>
@@ -14744,7 +14920,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>163</v>
+        <v>188</v>
       </c>
       <c r="C166">
         <v>717</v>
@@ -14824,7 +15000,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="C167">
         <v>667</v>
@@ -14904,7 +15080,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C168">
         <v>1048</v>
@@ -14984,7 +15160,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>166</v>
+        <v>191</v>
       </c>
       <c r="C169">
         <v>1116</v>
@@ -15064,7 +15240,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="C170">
         <v>1011</v>
@@ -15144,7 +15320,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>168</v>
+        <v>193</v>
       </c>
       <c r="C171">
         <v>912</v>
@@ -15224,7 +15400,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>169</v>
+        <v>194</v>
       </c>
       <c r="C172">
         <v>869</v>
@@ -15304,7 +15480,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>170</v>
+        <v>195</v>
       </c>
       <c r="C173">
         <v>783</v>
@@ -15384,7 +15560,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="C174">
         <v>768</v>
@@ -15464,7 +15640,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="C175">
         <v>926</v>
@@ -15544,7 +15720,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="C176">
         <v>856</v>
@@ -15624,7 +15800,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>174</v>
+        <v>199</v>
       </c>
       <c r="C177">
         <v>914</v>
@@ -15704,7 +15880,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="C178">
         <v>622</v>
@@ -15784,7 +15960,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>176</v>
+        <v>201</v>
       </c>
       <c r="C179">
         <v>592</v>
@@ -15864,7 +16040,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>177</v>
+        <v>202</v>
       </c>
       <c r="C180">
         <v>713</v>
@@ -15944,7 +16120,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>178</v>
+        <v>203</v>
       </c>
       <c r="C181">
         <v>338</v>
@@ -16024,7 +16200,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="C182">
         <v>552</v>
@@ -16104,7 +16280,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="C183">
         <v>767</v>
@@ -16184,7 +16360,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>181</v>
+        <v>206</v>
       </c>
       <c r="C184">
         <v>803</v>
@@ -16264,7 +16440,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="C185">
         <v>749</v>
@@ -16344,7 +16520,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>183</v>
+        <v>208</v>
       </c>
       <c r="C186">
         <v>742</v>
@@ -16424,7 +16600,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>184</v>
+        <v>209</v>
       </c>
       <c r="C187">
         <v>1140</v>
@@ -16504,7 +16680,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>185</v>
+        <v>210</v>
       </c>
       <c r="C188">
         <v>676</v>
@@ -16584,7 +16760,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>186</v>
+        <v>211</v>
       </c>
       <c r="C189">
         <v>720</v>
@@ -16664,7 +16840,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>187</v>
+        <v>212</v>
       </c>
       <c r="C190">
         <v>869</v>
@@ -16744,7 +16920,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>188</v>
+        <v>213</v>
       </c>
       <c r="C191">
         <v>932</v>
@@ -16824,7 +17000,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>189</v>
+        <v>214</v>
       </c>
       <c r="C192">
         <v>1014</v>
@@ -16904,7 +17080,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>190</v>
+        <v>215</v>
       </c>
       <c r="C193">
         <v>1021</v>
@@ -16984,7 +17160,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>191</v>
+        <v>216</v>
       </c>
       <c r="C194">
         <v>835</v>
@@ -17064,7 +17240,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="C195">
         <v>852</v>
@@ -17144,7 +17320,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="C196">
         <v>759</v>
@@ -17224,7 +17400,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="C197">
         <v>857</v>
@@ -17304,7 +17480,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>195</v>
+        <v>220</v>
       </c>
       <c r="C198">
         <v>784</v>
@@ -17384,7 +17560,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>196</v>
+        <v>221</v>
       </c>
       <c r="C199">
         <v>828</v>
@@ -17464,7 +17640,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="C200">
         <v>845</v>
@@ -17544,7 +17720,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="C201">
         <v>866</v>
@@ -17624,7 +17800,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>199</v>
+        <v>224</v>
       </c>
       <c r="C202">
         <v>411</v>
@@ -17704,7 +17880,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="C203">
         <v>939</v>
@@ -17784,7 +17960,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>201</v>
+        <v>226</v>
       </c>
       <c r="C204">
         <v>769</v>
@@ -17864,7 +18040,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>202</v>
+        <v>227</v>
       </c>
       <c r="C205">
         <v>527</v>
@@ -17944,7 +18120,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>203</v>
+        <v>228</v>
       </c>
       <c r="C206">
         <v>748</v>
@@ -18024,7 +18200,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>203</v>
+        <v>228</v>
       </c>
       <c r="C207">
         <v>619</v>
@@ -18104,7 +18280,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>204</v>
+        <v>229</v>
       </c>
       <c r="C208">
         <v>800</v>
@@ -18184,7 +18360,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>205</v>
+        <v>230</v>
       </c>
       <c r="C209">
         <v>856</v>
@@ -18264,7 +18440,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>206</v>
+        <v>231</v>
       </c>
       <c r="C210">
         <v>842</v>
@@ -18344,7 +18520,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>207</v>
+        <v>232</v>
       </c>
       <c r="C211">
         <v>580</v>
@@ -18424,7 +18600,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>208</v>
+        <v>233</v>
       </c>
       <c r="C212">
         <v>981</v>
@@ -18504,7 +18680,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>209</v>
+        <v>234</v>
       </c>
       <c r="C213">
         <v>989</v>
@@ -18584,7 +18760,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>210</v>
+        <v>235</v>
       </c>
       <c r="C214">
         <v>913</v>
@@ -18664,7 +18840,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>211</v>
+        <v>236</v>
       </c>
       <c r="C215">
         <v>706</v>
@@ -18744,7 +18920,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>212</v>
+        <v>237</v>
       </c>
       <c r="C216">
         <v>638</v>
@@ -18824,7 +19000,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>213</v>
+        <v>238</v>
       </c>
       <c r="C217">
         <v>1044</v>
@@ -18904,7 +19080,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>214</v>
+        <v>239</v>
       </c>
       <c r="C218">
         <v>1196</v>
@@ -18984,7 +19160,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>215</v>
+        <v>240</v>
       </c>
       <c r="C219">
         <v>1135</v>
@@ -19064,7 +19240,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="C220">
         <v>1017</v>
@@ -19144,7 +19320,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>217</v>
+        <v>242</v>
       </c>
       <c r="C221">
         <v>1069</v>
@@ -19224,7 +19400,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>218</v>
+        <v>243</v>
       </c>
       <c r="C222">
         <v>352</v>
@@ -19304,7 +19480,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>219</v>
+        <v>244</v>
       </c>
       <c r="C223">
         <v>712</v>
@@ -19384,7 +19560,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>220</v>
+        <v>245</v>
       </c>
       <c r="C224">
         <v>849</v>
@@ -19464,7 +19640,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>221</v>
+        <v>246</v>
       </c>
       <c r="C225">
         <v>522</v>
@@ -19544,7 +19720,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>222</v>
+        <v>247</v>
       </c>
       <c r="C226">
         <v>913</v>
@@ -19624,7 +19800,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>223</v>
+        <v>248</v>
       </c>
       <c r="C227">
         <v>621</v>
@@ -19704,7 +19880,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>224</v>
+        <v>249</v>
       </c>
       <c r="C228">
         <v>869</v>
@@ -19784,7 +19960,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="C229">
         <v>660</v>
@@ -19864,7 +20040,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="C230">
         <v>779</v>
@@ -19944,7 +20120,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>227</v>
+        <v>252</v>
       </c>
       <c r="C231">
         <v>1155</v>
@@ -20024,7 +20200,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>228</v>
+        <v>253</v>
       </c>
       <c r="C232">
         <v>1093</v>
@@ -20104,7 +20280,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>229</v>
+        <v>254</v>
       </c>
       <c r="C233">
         <v>700</v>
@@ -20184,7 +20360,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>230</v>
+        <v>255</v>
       </c>
       <c r="C234">
         <v>897</v>
@@ -20264,7 +20440,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>231</v>
+        <v>256</v>
       </c>
       <c r="C235">
         <v>876</v>
@@ -20344,7 +20520,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>232</v>
+        <v>257</v>
       </c>
       <c r="C236">
         <v>1002</v>
@@ -20424,7 +20600,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>233</v>
+        <v>258</v>
       </c>
       <c r="C237">
         <v>989</v>
@@ -20504,7 +20680,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>234</v>
+        <v>259</v>
       </c>
       <c r="C238">
         <v>824</v>
@@ -20584,7 +20760,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>235</v>
+        <v>260</v>
       </c>
       <c r="C239">
         <v>818</v>
@@ -20664,7 +20840,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>236</v>
+        <v>261</v>
       </c>
       <c r="C240">
         <v>1074</v>
@@ -20744,7 +20920,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>237</v>
+        <v>262</v>
       </c>
       <c r="C241">
         <v>948</v>
@@ -20824,7 +21000,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>238</v>
+        <v>263</v>
       </c>
       <c r="C242">
         <v>604</v>
@@ -20904,7 +21080,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>239</v>
+        <v>264</v>
       </c>
       <c r="C243">
         <v>929</v>
@@ -20984,7 +21160,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>240</v>
+        <v>265</v>
       </c>
       <c r="C244">
         <v>918</v>
@@ -21064,7 +21240,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>241</v>
+        <v>266</v>
       </c>
       <c r="C245">
         <v>393</v>
@@ -21144,7 +21320,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>242</v>
+        <v>267</v>
       </c>
       <c r="C246">
         <v>631</v>
@@ -21224,7 +21400,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>243</v>
+        <v>268</v>
       </c>
       <c r="C247">
         <v>634</v>
@@ -21304,7 +21480,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>244</v>
+        <v>269</v>
       </c>
       <c r="C248">
         <v>566</v>
@@ -21384,7 +21560,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="C249">
         <v>598</v>
@@ -21464,7 +21640,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="C250">
         <v>964</v>
@@ -21544,7 +21720,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>247</v>
+        <v>272</v>
       </c>
       <c r="C251">
         <v>739</v>
@@ -21624,7 +21800,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>248</v>
+        <v>273</v>
       </c>
       <c r="C252">
         <v>633</v>
@@ -21704,7 +21880,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>249</v>
+        <v>274</v>
       </c>
       <c r="C253">
         <v>845</v>
@@ -21784,7 +21960,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="C254">
         <v>1050</v>
@@ -21864,7 +22040,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="C255">
         <v>886</v>
@@ -21944,7 +22120,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="C256">
         <v>863</v>
@@ -22024,7 +22200,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>253</v>
+        <v>278</v>
       </c>
       <c r="C257">
         <v>704</v>
@@ -22104,7 +22280,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>254</v>
+        <v>279</v>
       </c>
       <c r="C258">
         <v>716</v>
@@ -22184,7 +22360,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>255</v>
+        <v>280</v>
       </c>
       <c r="C259">
         <v>1021</v>
@@ -22264,7 +22440,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>256</v>
+        <v>281</v>
       </c>
       <c r="C260">
         <v>483</v>
@@ -22344,7 +22520,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>257</v>
+        <v>282</v>
       </c>
       <c r="C261">
         <v>961</v>
@@ -22424,7 +22600,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>258</v>
+        <v>283</v>
       </c>
       <c r="C262">
         <v>1214</v>
@@ -22504,7 +22680,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>259</v>
+        <v>284</v>
       </c>
       <c r="C263">
         <v>1062</v>
@@ -22584,7 +22760,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>260</v>
+        <v>285</v>
       </c>
       <c r="C264">
         <v>900</v>
@@ -22664,7 +22840,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>261</v>
+        <v>286</v>
       </c>
       <c r="C265">
         <v>699</v>
@@ -22744,7 +22920,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>262</v>
+        <v>287</v>
       </c>
       <c r="C266">
         <v>467</v>
@@ -22824,7 +23000,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>263</v>
+        <v>288</v>
       </c>
       <c r="C267">
         <v>643</v>
@@ -22904,7 +23080,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>264</v>
+        <v>289</v>
       </c>
       <c r="C268">
         <v>681</v>
@@ -22984,7 +23160,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>265</v>
+        <v>290</v>
       </c>
       <c r="C269">
         <v>495</v>
@@ -23064,7 +23240,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>266</v>
+        <v>291</v>
       </c>
       <c r="C270">
         <v>874</v>
@@ -23144,7 +23320,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>267</v>
+        <v>292</v>
       </c>
       <c r="C271">
         <v>724</v>
@@ -23224,7 +23400,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>268</v>
+        <v>293</v>
       </c>
       <c r="C272">
         <v>1141</v>
@@ -23304,7 +23480,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>269</v>
+        <v>294</v>
       </c>
       <c r="C273">
         <v>482</v>
@@ -23384,7 +23560,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>270</v>
+        <v>295</v>
       </c>
       <c r="C274">
         <v>917</v>
@@ -23464,7 +23640,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>271</v>
+        <v>296</v>
       </c>
       <c r="C275">
         <v>823</v>
@@ -23544,7 +23720,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>272</v>
+        <v>297</v>
       </c>
       <c r="C276">
         <v>718</v>
@@ -23624,7 +23800,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>273</v>
+        <v>298</v>
       </c>
       <c r="C277">
         <v>922</v>
@@ -23704,7 +23880,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>274</v>
+        <v>299</v>
       </c>
       <c r="C278">
         <v>951</v>
@@ -23784,7 +23960,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="C279">
         <v>550</v>
@@ -23864,7 +24040,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>276</v>
+        <v>301</v>
       </c>
       <c r="C280">
         <v>688</v>
@@ -23944,7 +24120,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>277</v>
+        <v>302</v>
       </c>
       <c r="C281">
         <v>641</v>
@@ -24024,7 +24200,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>278</v>
+        <v>303</v>
       </c>
       <c r="C282">
         <v>762</v>
@@ -24104,7 +24280,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>279</v>
+        <v>304</v>
       </c>
       <c r="C283">
         <v>662</v>
@@ -24184,7 +24360,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="C284">
         <v>638</v>
@@ -24264,7 +24440,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>281</v>
+        <v>306</v>
       </c>
       <c r="C285">
         <v>672</v>
@@ -24344,7 +24520,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>282</v>
+        <v>307</v>
       </c>
       <c r="C286">
         <v>838</v>
@@ -24424,7 +24600,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>283</v>
+        <v>308</v>
       </c>
       <c r="C287">
         <v>942</v>
@@ -24504,7 +24680,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="C288">
         <v>1208</v>
@@ -24584,7 +24760,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="C289">
         <v>1147</v>
@@ -24664,7 +24840,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="C290">
         <v>1058</v>
@@ -24744,7 +24920,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>287</v>
+        <v>312</v>
       </c>
       <c r="C291">
         <v>888</v>
@@ -24824,7 +25000,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>288</v>
+        <v>313</v>
       </c>
       <c r="C292">
         <v>406</v>
@@ -24904,7 +25080,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>289</v>
+        <v>314</v>
       </c>
       <c r="C293">
         <v>909</v>
@@ -24984,7 +25160,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="C294">
         <v>807</v>
@@ -25064,7 +25240,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>291</v>
+        <v>316</v>
       </c>
       <c r="C295">
         <v>1080</v>
@@ -25144,7 +25320,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>292</v>
+        <v>317</v>
       </c>
       <c r="C296">
         <v>805</v>
@@ -25224,7 +25400,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
       <c r="C297">
         <v>1212</v>
@@ -25304,7 +25480,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>294</v>
+        <v>319</v>
       </c>
       <c r="C298">
         <v>818</v>
@@ -25384,7 +25560,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>295</v>
+        <v>320</v>
       </c>
       <c r="C299">
         <v>720</v>
@@ -25464,7 +25640,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>296</v>
+        <v>321</v>
       </c>
       <c r="C300">
         <v>868</v>
@@ -25544,7 +25720,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>297</v>
+        <v>322</v>
       </c>
       <c r="C301">
         <v>841</v>
@@ -25624,7 +25800,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>298</v>
+        <v>323</v>
       </c>
       <c r="C302">
         <v>796</v>
@@ -25704,7 +25880,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>299</v>
+        <v>324</v>
       </c>
       <c r="C303">
         <v>770</v>
@@ -25784,7 +25960,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="C304">
         <v>1060</v>
@@ -25864,7 +26040,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>301</v>
+        <v>326</v>
       </c>
       <c r="C305">
         <v>943</v>
@@ -25944,7 +26120,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>302</v>
+        <v>327</v>
       </c>
       <c r="C306">
         <v>1078</v>
@@ -26024,7 +26200,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>303</v>
+        <v>328</v>
       </c>
       <c r="C307">
         <v>959</v>
@@ -26104,7 +26280,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>304</v>
+        <v>329</v>
       </c>
       <c r="C308">
         <v>508</v>
@@ -26184,7 +26360,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>305</v>
+        <v>330</v>
       </c>
       <c r="C309">
         <v>685</v>
@@ -26264,7 +26440,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>306</v>
+        <v>331</v>
       </c>
       <c r="C310">
         <v>633</v>
@@ -26344,7 +26520,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>307</v>
+        <v>332</v>
       </c>
       <c r="C311">
         <v>859</v>
@@ -26424,7 +26600,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>308</v>
+        <v>333</v>
       </c>
       <c r="C312">
         <v>1103</v>
@@ -26504,7 +26680,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>309</v>
+        <v>334</v>
       </c>
       <c r="C313">
         <v>529</v>
@@ -26584,7 +26760,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>310</v>
+        <v>335</v>
       </c>
       <c r="C314">
         <v>840</v>
@@ -26664,7 +26840,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>311</v>
+        <v>336</v>
       </c>
       <c r="C315">
         <v>759</v>
@@ -26744,7 +26920,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>312</v>
+        <v>337</v>
       </c>
       <c r="C316">
         <v>853</v>
@@ -26824,7 +27000,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>313</v>
+        <v>338</v>
       </c>
       <c r="C317">
         <v>831</v>
@@ -26904,7 +27080,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>314</v>
+        <v>339</v>
       </c>
       <c r="C318">
         <v>1047</v>
@@ -26984,7 +27160,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
       <c r="C319">
         <v>721</v>
@@ -27064,7 +27240,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>316</v>
+        <v>341</v>
       </c>
       <c r="C320">
         <v>653</v>
@@ -27144,7 +27320,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>317</v>
+        <v>342</v>
       </c>
       <c r="C321">
         <v>780</v>
@@ -27224,7 +27400,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>318</v>
+        <v>343</v>
       </c>
       <c r="C322">
         <v>713</v>
@@ -27304,7 +27480,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>319</v>
+        <v>344</v>
       </c>
       <c r="C323">
         <v>1198</v>
@@ -27384,7 +27560,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>320</v>
+        <v>345</v>
       </c>
       <c r="C324">
         <v>890</v>
@@ -27464,7 +27640,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>321</v>
+        <v>346</v>
       </c>
       <c r="C325">
         <v>1100</v>
@@ -27544,7 +27720,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="C326">
         <v>733</v>
@@ -27624,7 +27800,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>323</v>
+        <v>348</v>
       </c>
       <c r="C327">
         <v>787</v>
@@ -27704,7 +27880,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>324</v>
+        <v>349</v>
       </c>
       <c r="C328">
         <v>973</v>
@@ -27784,7 +27960,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="C329">
         <v>943</v>
@@ -27864,7 +28040,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>326</v>
+        <v>351</v>
       </c>
       <c r="C330">
         <v>667</v>
@@ -27944,7 +28120,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>327</v>
+        <v>352</v>
       </c>
       <c r="C331">
         <v>636</v>
@@ -28024,7 +28200,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>328</v>
+        <v>353</v>
       </c>
       <c r="C332">
         <v>657</v>
@@ -28104,7 +28280,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>329</v>
+        <v>354</v>
       </c>
       <c r="C333">
         <v>975</v>
@@ -28184,7 +28360,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>330</v>
+        <v>355</v>
       </c>
       <c r="C334">
         <v>1203</v>
@@ -28264,7 +28440,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>331</v>
+        <v>356</v>
       </c>
       <c r="C335">
         <v>913</v>
@@ -28344,7 +28520,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>332</v>
+        <v>357</v>
       </c>
       <c r="C336">
         <v>1139</v>
@@ -28424,7 +28600,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>333</v>
+        <v>358</v>
       </c>
       <c r="C337">
         <v>1124</v>
@@ -28504,7 +28680,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>334</v>
+        <v>359</v>
       </c>
       <c r="C338">
         <v>1030</v>
@@ -28584,7 +28760,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>335</v>
+        <v>360</v>
       </c>
       <c r="C339">
         <v>923</v>
@@ -28664,7 +28840,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>336</v>
+        <v>361</v>
       </c>
       <c r="C340">
         <v>972</v>
@@ -28744,7 +28920,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>337</v>
+        <v>362</v>
       </c>
       <c r="C341">
         <v>696</v>
@@ -28824,7 +29000,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>338</v>
+        <v>363</v>
       </c>
       <c r="C342">
         <v>837</v>
@@ -28904,7 +29080,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>339</v>
+        <v>364</v>
       </c>
       <c r="C343">
         <v>652</v>
@@ -28984,7 +29160,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>340</v>
+        <v>365</v>
       </c>
       <c r="C344">
         <v>608</v>
@@ -29064,7 +29240,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>341</v>
+        <v>366</v>
       </c>
       <c r="C345">
         <v>594</v>
@@ -29144,7 +29320,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>342</v>
+        <v>367</v>
       </c>
       <c r="C346">
         <v>777</v>
@@ -29224,7 +29400,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>343</v>
+        <v>368</v>
       </c>
       <c r="C347">
         <v>723</v>
@@ -29304,7 +29480,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>344</v>
+        <v>369</v>
       </c>
       <c r="C348">
         <v>669</v>
@@ -29384,7 +29560,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>345</v>
+        <v>370</v>
       </c>
       <c r="C349">
         <v>827</v>
@@ -29464,7 +29640,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>346</v>
+        <v>371</v>
       </c>
       <c r="C350">
         <v>905</v>
@@ -29544,7 +29720,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>347</v>
+        <v>372</v>
       </c>
       <c r="C351">
         <v>1024</v>
@@ -29624,7 +29800,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>348</v>
+        <v>373</v>
       </c>
       <c r="C352">
         <v>946</v>
@@ -29704,7 +29880,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>349</v>
+        <v>374</v>
       </c>
       <c r="C353">
         <v>467</v>
@@ -29784,7 +29960,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="C354">
         <v>766</v>
@@ -29864,7 +30040,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>351</v>
+        <v>376</v>
       </c>
       <c r="C355">
         <v>950</v>
@@ -29944,7 +30120,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>352</v>
+        <v>377</v>
       </c>
       <c r="C356">
         <v>1009</v>
@@ -30024,7 +30200,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>353</v>
+        <v>378</v>
       </c>
       <c r="C357">
         <v>1119</v>
@@ -30104,7 +30280,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>354</v>
+        <v>379</v>
       </c>
       <c r="C358">
         <v>1215</v>
@@ -30184,7 +30360,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>355</v>
+        <v>380</v>
       </c>
       <c r="C359">
         <v>1050</v>
@@ -30264,7 +30440,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="C360">
         <v>1105</v>
@@ -30344,7 +30520,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>357</v>
+        <v>382</v>
       </c>
       <c r="C361">
         <v>1097</v>
@@ -30424,7 +30600,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>358</v>
+        <v>383</v>
       </c>
       <c r="C362">
         <v>1142</v>
@@ -30504,7 +30680,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>359</v>
+        <v>384</v>
       </c>
       <c r="C363">
         <v>676</v>
@@ -30584,7 +30760,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>360</v>
+        <v>385</v>
       </c>
       <c r="C364">
         <v>1065</v>
@@ -30664,7 +30840,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>361</v>
+        <v>386</v>
       </c>
       <c r="C365">
         <v>797</v>
@@ -30744,7 +30920,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>362</v>
+        <v>387</v>
       </c>
       <c r="C366">
         <v>933</v>
@@ -30824,7 +31000,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>363</v>
+        <v>388</v>
       </c>
       <c r="C367">
         <v>819</v>
@@ -30904,7 +31080,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>364</v>
+        <v>389</v>
       </c>
       <c r="C368">
         <v>994</v>
@@ -30984,7 +31160,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>365</v>
+        <v>390</v>
       </c>
       <c r="C369">
         <v>737</v>
@@ -31064,7 +31240,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>366</v>
+        <v>391</v>
       </c>
       <c r="C370">
         <v>697</v>
@@ -31144,7 +31320,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>367</v>
+        <v>392</v>
       </c>
       <c r="C371">
         <v>717</v>
@@ -31224,7 +31400,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>368</v>
+        <v>393</v>
       </c>
       <c r="C372">
         <v>717</v>
@@ -31304,7 +31480,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>369</v>
+        <v>394</v>
       </c>
       <c r="C373">
         <v>834</v>
@@ -31384,7 +31560,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>370</v>
+        <v>395</v>
       </c>
       <c r="C374">
         <v>853</v>
@@ -31464,7 +31640,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>371</v>
+        <v>396</v>
       </c>
       <c r="C375">
         <v>843</v>
@@ -31544,7 +31720,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>372</v>
+        <v>397</v>
       </c>
       <c r="C376">
         <v>531</v>
@@ -31624,7 +31800,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="C377">
         <v>833</v>
@@ -31704,7 +31880,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>373</v>
+        <v>398</v>
       </c>
       <c r="C378">
         <v>937</v>
@@ -31784,7 +31960,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>374</v>
+        <v>399</v>
       </c>
       <c r="C379">
         <v>807</v>
@@ -31864,7 +32040,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>375</v>
+        <v>400</v>
       </c>
       <c r="C380">
         <v>623</v>
@@ -31944,7 +32120,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>376</v>
+        <v>401</v>
       </c>
       <c r="C381">
         <v>976</v>
@@ -32024,7 +32200,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>377</v>
+        <v>402</v>
       </c>
       <c r="C382">
         <v>670</v>
@@ -32104,7 +32280,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>378</v>
+        <v>403</v>
       </c>
       <c r="C383">
         <v>659</v>
@@ -32184,7 +32360,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>379</v>
+        <v>404</v>
       </c>
       <c r="C384">
         <v>1028</v>
@@ -32264,7 +32440,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>380</v>
+        <v>405</v>
       </c>
       <c r="C385">
         <v>1123</v>
@@ -32344,7 +32520,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>381</v>
+        <v>406</v>
       </c>
       <c r="C386">
         <v>785</v>
@@ -32424,7 +32600,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>382</v>
+        <v>407</v>
       </c>
       <c r="C387">
         <v>823</v>
@@ -32504,7 +32680,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>383</v>
+        <v>408</v>
       </c>
       <c r="C388">
         <v>784</v>
@@ -32584,7 +32760,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>384</v>
+        <v>409</v>
       </c>
       <c r="C389">
         <v>845</v>
@@ -32664,7 +32840,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>385</v>
+        <v>410</v>
       </c>
       <c r="C390">
         <v>790</v>
@@ -32744,7 +32920,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>386</v>
+        <v>411</v>
       </c>
       <c r="C391">
         <v>1061</v>
@@ -32824,7 +33000,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>387</v>
+        <v>412</v>
       </c>
       <c r="C392">
         <v>695</v>
@@ -32904,7 +33080,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>388</v>
+        <v>413</v>
       </c>
       <c r="C393">
         <v>505</v>
@@ -32984,7 +33160,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>389</v>
+        <v>414</v>
       </c>
       <c r="C394">
         <v>767</v>
@@ -33064,7 +33240,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>390</v>
+        <v>415</v>
       </c>
       <c r="C395">
         <v>904</v>
@@ -33144,7 +33320,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>391</v>
+        <v>416</v>
       </c>
       <c r="C396">
         <v>1074</v>
@@ -33224,7 +33400,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>392</v>
+        <v>417</v>
       </c>
       <c r="C397">
         <v>544</v>
@@ -33304,7 +33480,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>393</v>
+        <v>418</v>
       </c>
       <c r="C398">
         <v>635</v>
@@ -33384,7 +33560,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>394</v>
+        <v>419</v>
       </c>
       <c r="C399">
         <v>603</v>
@@ -33464,7 +33640,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>395</v>
+        <v>420</v>
       </c>
       <c r="C400">
         <v>945</v>
@@ -33544,7 +33720,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>396</v>
+        <v>421</v>
       </c>
       <c r="C401">
         <v>811</v>
@@ -33624,7 +33800,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>397</v>
+        <v>422</v>
       </c>
       <c r="C402">
         <v>1150</v>
@@ -33704,7 +33880,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>398</v>
+        <v>423</v>
       </c>
       <c r="C403">
         <v>1066</v>
